--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -31,10 +31,10 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>UI/UX Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC001: Verify consistency of font styles across Web screens </t>
+    <t>Web UI/UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC001: Verify responsive grid layout </t>
   </si>
   <si>
     <t>PASS</t>
@@ -43,916 +43,916 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 3:55:25 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC002: Verify color contrast for readability in dark mode </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC003: Verify button hover effects and animations </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC004: Verify clear error messages for invalid inputs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC005: Verify smooth transitions between dashboard tabs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC006: Verify image loading placeholders for menu items </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC007: Verify form field alignment on checkout page </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC008: Verify dark mode UI consistency </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC009: Verify glassmorphism effect on cards </t>
-  </si>
-  <si>
-    <t>TC010: Verify consistency of font styles across Web screens (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC011: Verify color contrast for readability in dark mode (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC012: Verify button hover effects and animations (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC013: Verify clear error messages for invalid inputs (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC014: Verify smooth transitions between dashboard tabs (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC015: Verify image loading placeholders for menu items (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC016: Verify form field alignment on checkout page (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC017: Verify dark mode UI consistency (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC018: Verify glassmorphism effect on cards (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC019: Verify consistency of font styles across Web screens (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC020: Verify color contrast for readability in dark mode (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC021: Verify button hover effects and animations (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC022: Verify clear error messages for invalid inputs (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC023: Verify smooth transitions between dashboard tabs (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC024: Verify image loading placeholders for menu items (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC025: Verify form field alignment on checkout page (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC026: Verify dark mode UI consistency (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC027: Verify glassmorphism effect on cards (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC028: Verify consistency of font styles across Web screens (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC029: Verify color contrast for readability in dark mode (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC030: Verify button hover effects and animations (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC031: Verify clear error messages for invalid inputs (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC032: Verify smooth transitions between dashboard tabs (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC033: Verify image loading placeholders for menu items (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC034: Verify form field alignment on checkout page (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC035: Verify dark mode UI consistency (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC036: Verify glassmorphism effect on cards (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC037: Verify consistency of font styles across Web screens (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC038: Verify color contrast for readability in dark mode (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC039: Verify button hover effects and animations (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC040: Verify clear error messages for invalid inputs (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC041: Verify smooth transitions between dashboard tabs (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC042: Verify image loading placeholders for menu items (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC043: Verify form field alignment on checkout page (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC044: Verify dark mode UI consistency (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC045: Verify glassmorphism effect on cards (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC046: Verify consistency of font styles across Web screens (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC047: Verify color contrast for readability in dark mode (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC048: Verify button hover effects and animations (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC049: Verify clear error messages for invalid inputs (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC050: Verify smooth transitions between dashboard tabs (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC051: Verify image loading placeholders for menu items (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC052: Verify form field alignment on checkout page (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC053: Verify dark mode UI consistency (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC054: Verify glassmorphism effect on cards (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC055: Verify consistency of font styles across Web screens (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC056: Verify color contrast for readability in dark mode (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC057: Verify button hover effects and animations (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC058: Verify clear error messages for invalid inputs (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC059: Verify smooth transitions between dashboard tabs (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC060: Verify image loading placeholders for menu items (Variation 7)</t>
-  </si>
-  <si>
-    <t>Compatibility Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC061: Verify app behavior on small screens </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC062: Verify app behavior on tablets/large screens </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC063: Verify app compatibility with latest OS version </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC064: Verify app compatibility with older OS versions </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC065: Verify app behavior on different aspect ratios </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC066: Verify app fonts scaling with system settings </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC067: Verify background tasks on low-end hardware </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC068: Verify app launch time on cold start </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC069: Verify interaction with system navigation gestures </t>
-  </si>
-  <si>
-    <t>TC070: Verify app behavior on small screens (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC071: Verify app behavior on tablets/large screens (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC072: Verify app compatibility with latest OS version (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC073: Verify app compatibility with older OS versions (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC074: Verify app behavior on different aspect ratios (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC075: Verify app fonts scaling with system settings (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC076: Verify background tasks on low-end hardware (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC077: Verify app launch time on cold start (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC078: Verify interaction with system navigation gestures (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC079: Verify app behavior on small screens (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC080: Verify app behavior on tablets/large screens (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC081: Verify app compatibility with latest OS version (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC082: Verify app compatibility with older OS versions (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC083: Verify app behavior on different aspect ratios (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC084: Verify app fonts scaling with system settings (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC085: Verify background tasks on low-end hardware (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC086: Verify app launch time on cold start (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC087: Verify interaction with system navigation gestures (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC088: Verify app behavior on small screens (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC089: Verify app behavior on tablets/large screens (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC090: Verify app compatibility with latest OS version (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC091: Verify app compatibility with older OS versions (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC092: Verify app behavior on different aspect ratios (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC093: Verify app fonts scaling with system settings (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC094: Verify background tasks on low-end hardware (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC095: Verify app launch time on cold start (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC096: Verify interaction with system navigation gestures (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC097: Verify app behavior on small screens (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC098: Verify app behavior on tablets/large screens (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC099: Verify app compatibility with latest OS version (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC100: Verify app compatibility with older OS versions (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC101: Verify app behavior on different aspect ratios (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC102: Verify app fonts scaling with system settings (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC103: Verify background tasks on low-end hardware (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC104: Verify app launch time on cold start (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC105: Verify interaction with system navigation gestures (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC106: Verify app behavior on small screens (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC107: Verify app behavior on tablets/large screens (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC108: Verify app compatibility with latest OS version (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC109: Verify app compatibility with older OS versions (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC110: Verify app behavior on different aspect ratios (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC111: Verify app fonts scaling with system settings (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC112: Verify background tasks on low-end hardware (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC113: Verify app launch time on cold start (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC114: Verify interaction with system navigation gestures (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC115: Verify app behavior on small screens (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC116: Verify app behavior on tablets/large screens (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC117: Verify app compatibility with latest OS version (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC118: Verify app compatibility with older OS versions (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC119: Verify app behavior on different aspect ratios (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC120: Verify app fonts scaling with system settings (Variation 7)</t>
-  </si>
-  <si>
-    <t>Accessibility Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC121: Verify screen reader support for all flows </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC122: Verify touch target sizes meet standards </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC123: Verify high contrast theme support </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC124: Verify text scaling without layout breakage </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC125: Verify descriptive alt text for images </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC126: Verify focus indicators for interactive elements </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC127: Verify keyboard navigation support </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC128: Verify captions for any video content </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC129: Verify clear error announcements to screen reader </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC130: Verify accessible names for icons </t>
-  </si>
-  <si>
-    <t>TC131: Verify screen reader support for all flows (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC132: Verify touch target sizes meet standards (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC133: Verify high contrast theme support (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC134: Verify text scaling without layout breakage (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC135: Verify descriptive alt text for images (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC136: Verify focus indicators for interactive elements (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC137: Verify keyboard navigation support (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC138: Verify captions for any video content (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC139: Verify clear error announcements to screen reader (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC140: Verify accessible names for icons (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC141: Verify screen reader support for all flows (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC142: Verify touch target sizes meet standards (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC143: Verify high contrast theme support (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC144: Verify text scaling without layout breakage (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC145: Verify descriptive alt text for images (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC146: Verify focus indicators for interactive elements (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC147: Verify keyboard navigation support (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC148: Verify captions for any video content (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC149: Verify clear error announcements to screen reader (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC150: Verify accessible names for icons (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC151: Verify screen reader support for all flows (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC152: Verify touch target sizes meet standards (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC153: Verify high contrast theme support (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC154: Verify text scaling without layout breakage (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC155: Verify descriptive alt text for images (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC156: Verify focus indicators for interactive elements (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC157: Verify keyboard navigation support (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC158: Verify captions for any video content (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC159: Verify clear error announcements to screen reader (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC160: Verify accessible names for icons (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC161: Verify screen reader support for all flows (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC162: Verify touch target sizes meet standards (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC163: Verify high contrast theme support (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC164: Verify text scaling without layout breakage (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC165: Verify descriptive alt text for images (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC166: Verify focus indicators for interactive elements (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC167: Verify keyboard navigation support (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC168: Verify captions for any video content (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC169: Verify clear error announcements to screen reader (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC170: Verify accessible names for icons (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC171: Verify screen reader support for all flows (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC172: Verify touch target sizes meet standards (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC173: Verify high contrast theme support (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC174: Verify text scaling without layout breakage (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC175: Verify descriptive alt text for images (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC176: Verify focus indicators for interactive elements (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC177: Verify keyboard navigation support (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC178: Verify captions for any video content (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC179: Verify clear error announcements to screen reader (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC180: Verify accessible names for icons (Variation 6)</t>
-  </si>
-  <si>
-    <t>Platform-Specific Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC181: Verify app behavior on incoming calls </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC182: Verify app behavior during network switch </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC183: Verify push notification click-through behavior </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC184: Verify app state preservation during backgrounding </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC185: Verify camera integration for profile picture </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC186: Verify location permission handling </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC187: Verify deep link processing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC188: Verify orientation change handling </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC189: Verify offline data sync functionality </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC190: Verify app interaction with other system apps </t>
-  </si>
-  <si>
-    <t>TC191: Verify app behavior on incoming calls (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC192: Verify app behavior during network switch (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC193: Verify push notification click-through behavior (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC194: Verify app state preservation during backgrounding (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC195: Verify camera integration for profile picture (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC196: Verify location permission handling (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC197: Verify deep link processing (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC198: Verify orientation change handling (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC199: Verify offline data sync functionality (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC200: Verify app interaction with other system apps (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC201: Verify app behavior on incoming calls (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC202: Verify app behavior during network switch (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC203: Verify push notification click-through behavior (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC204: Verify app state preservation during backgrounding (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC205: Verify camera integration for profile picture (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC206: Verify location permission handling (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC207: Verify deep link processing (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC208: Verify orientation change handling (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC209: Verify offline data sync functionality (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC210: Verify app interaction with other system apps (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC211: Verify app behavior on incoming calls (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC212: Verify app behavior during network switch (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC213: Verify push notification click-through behavior (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC214: Verify app state preservation during backgrounding (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC215: Verify camera integration for profile picture (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC216: Verify location permission handling (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC217: Verify deep link processing (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC218: Verify orientation change handling (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC219: Verify offline data sync functionality (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC220: Verify app interaction with other system apps (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC221: Verify app behavior on incoming calls (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC222: Verify app behavior during network switch (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC223: Verify push notification click-through behavior (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC224: Verify app state preservation during backgrounding (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC225: Verify camera integration for profile picture (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC226: Verify location permission handling (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC227: Verify deep link processing (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC228: Verify orientation change handling (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC229: Verify offline data sync functionality (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC230: Verify app interaction with other system apps (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC231: Verify app behavior on incoming calls (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC232: Verify app behavior during network switch (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC233: Verify push notification click-through behavior (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC234: Verify app state preservation during backgrounding (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC235: Verify camera integration for profile picture (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC236: Verify location permission handling (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC237: Verify deep link processing (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC238: Verify orientation change handling (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC239: Verify offline data sync functionality (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC240: Verify app interaction with other system apps (Variation 6)</t>
-  </si>
-  <si>
-    <t>End-to-End Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC241: Full Flow: User login, add to cart, and checkout </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC242: Full Flow: Admin dashboard monitoring to order approval </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC243: Full Flow: Guest search to login prompt to ordering </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC244: Full Flow: Payment gateway processing and confirmation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC245: Full Flow: Order status tracking from placed to delivered </t>
-  </si>
-  <si>
-    <t>TC246: Full Flow: User login, add to cart, and checkout (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC247: Full Flow: Admin dashboard monitoring to order approval (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC248: Full Flow: Guest search to login prompt to ordering (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC249: Full Flow: Payment gateway processing and confirmation (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC250: Full Flow: Order status tracking from placed to delivered (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC251: Full Flow: User login, add to cart, and checkout (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC252: Full Flow: Admin dashboard monitoring to order approval (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC253: Full Flow: Guest search to login prompt to ordering (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC254: Full Flow: Payment gateway processing and confirmation (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC255: Full Flow: Order status tracking from placed to delivered (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC256: Full Flow: User login, add to cart, and checkout (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC257: Full Flow: Admin dashboard monitoring to order approval (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC258: Full Flow: Guest search to login prompt to ordering (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC259: Full Flow: Payment gateway processing and confirmation (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC260: Full Flow: Order status tracking from placed to delivered (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC261: Full Flow: User login, add to cart, and checkout (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC262: Full Flow: Admin dashboard monitoring to order approval (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC263: Full Flow: Guest search to login prompt to ordering (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC264: Full Flow: Payment gateway processing and confirmation (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC265: Full Flow: Order status tracking from placed to delivered (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC266: Full Flow: User login, add to cart, and checkout (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC267: Full Flow: Admin dashboard monitoring to order approval (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC268: Full Flow: Guest search to login prompt to ordering (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC269: Full Flow: Payment gateway processing and confirmation (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC270: Full Flow: Order status tracking from placed to delivered (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC271: Full Flow: User login, add to cart, and checkout (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC272: Full Flow: Admin dashboard monitoring to order approval (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC273: Full Flow: Guest search to login prompt to ordering (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC274: Full Flow: Payment gateway processing and confirmation (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC275: Full Flow: Order status tracking from placed to delivered (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC276: Full Flow: User login, add to cart, and checkout (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC277: Full Flow: Admin dashboard monitoring to order approval (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC278: Full Flow: Guest search to login prompt to ordering (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC279: Full Flow: Payment gateway processing and confirmation (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC280: Full Flow: Order status tracking from placed to delivered (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC281: Full Flow: User login, add to cart, and checkout (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC282: Full Flow: Admin dashboard monitoring to order approval (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC283: Full Flow: Guest search to login prompt to ordering (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC284: Full Flow: Payment gateway processing and confirmation (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC285: Full Flow: Order status tracking from placed to delivered (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC286: Full Flow: User login, add to cart, and checkout (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC287: Full Flow: Admin dashboard monitoring to order approval (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC288: Full Flow: Guest search to login prompt to ordering (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC289: Full Flow: Payment gateway processing and confirmation (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC290: Full Flow: Order status tracking from placed to delivered (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC291: Full Flow: User login, add to cart, and checkout (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC292: Full Flow: Admin dashboard monitoring to order approval (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC293: Full Flow: Guest search to login prompt to ordering (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC294: Full Flow: Payment gateway processing and confirmation (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC295: Full Flow: Order status tracking from placed to delivered (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC296: Full Flow: User login, add to cart, and checkout (Variation 12)</t>
-  </si>
-  <si>
-    <t>TC297: Full Flow: Admin dashboard monitoring to order approval (Variation 12)</t>
-  </si>
-  <si>
-    <t>TC298: Full Flow: Guest search to login prompt to ordering (Variation 12)</t>
-  </si>
-  <si>
-    <t>TC299: Full Flow: Payment gateway processing and confirmation (Variation 12)</t>
-  </si>
-  <si>
-    <t>TC300: Full Flow: Order status tracking from placed to delivered (Variation 12)</t>
+    <t>8/7/2026, 4:01:40 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC002: Verify hover states on buttons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC003: Verify modal popups close </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC004: Verify forms inline validation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC005: Verify mega menu dropdown </t>
+  </si>
+  <si>
+    <t>TC006: Verify responsive grid layout (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC007: Verify hover states on buttons (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC008: Verify modal popups close (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC009: Verify forms inline validation (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC010: Verify mega menu dropdown (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC011: Verify responsive grid layout (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC012: Verify hover states on buttons (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC013: Verify modal popups close (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC014: Verify forms inline validation (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC015: Verify mega menu dropdown (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC016: Verify responsive grid layout (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC017: Verify hover states on buttons (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC018: Verify modal popups close (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC019: Verify forms inline validation (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC020: Verify mega menu dropdown (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC021: Verify responsive grid layout (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC022: Verify hover states on buttons (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC023: Verify modal popups close (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC024: Verify forms inline validation (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC025: Verify mega menu dropdown (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC026: Verify responsive grid layout (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC027: Verify hover states on buttons (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC028: Verify modal popups close (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC029: Verify forms inline validation (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC030: Verify mega menu dropdown (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC031: Verify responsive grid layout (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC032: Verify hover states on buttons (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC033: Verify modal popups close (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC034: Verify forms inline validation (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC035: Verify mega menu dropdown (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC036: Verify responsive grid layout (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC037: Verify hover states on buttons (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC038: Verify modal popups close (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC039: Verify forms inline validation (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC040: Verify mega menu dropdown (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC041: Verify responsive grid layout (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC042: Verify hover states on buttons (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC043: Verify modal popups close (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC044: Verify forms inline validation (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC045: Verify mega menu dropdown (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC046: Verify responsive grid layout (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC047: Verify hover states on buttons (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC048: Verify modal popups close (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC049: Verify forms inline validation (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC050: Verify mega menu dropdown (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC051: Verify responsive grid layout (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC052: Verify hover states on buttons (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC053: Verify modal popups close (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC054: Verify forms inline validation (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC055: Verify mega menu dropdown (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC056: Verify responsive grid layout (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC057: Verify hover states on buttons (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC058: Verify modal popups close (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC059: Verify forms inline validation (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC060: Verify mega menu dropdown (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Browser Compatibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC061: Verify app on Chrome v120+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC062: Verify app on Firefox </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC063: Verify app on Safari (macOS) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC064: Verify app on Edge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC065: Verify mobile-web viewport scaling </t>
+  </si>
+  <si>
+    <t>TC066: Verify app on Chrome v120+ (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC067: Verify app on Firefox (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC068: Verify app on Safari (macOS) (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC069: Verify app on Edge (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC070: Verify mobile-web viewport scaling (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC071: Verify app on Chrome v120+ (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC072: Verify app on Firefox (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC073: Verify app on Safari (macOS) (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC074: Verify app on Edge (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC075: Verify mobile-web viewport scaling (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC076: Verify app on Chrome v120+ (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC077: Verify app on Firefox (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC078: Verify app on Safari (macOS) (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC079: Verify app on Edge (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC080: Verify mobile-web viewport scaling (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC081: Verify app on Chrome v120+ (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC082: Verify app on Firefox (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC083: Verify app on Safari (macOS) (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC084: Verify app on Edge (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC085: Verify mobile-web viewport scaling (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC086: Verify app on Chrome v120+ (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC087: Verify app on Firefox (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC088: Verify app on Safari (macOS) (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC089: Verify app on Edge (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC090: Verify mobile-web viewport scaling (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC091: Verify app on Chrome v120+ (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC092: Verify app on Firefox (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC093: Verify app on Safari (macOS) (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC094: Verify app on Edge (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC095: Verify mobile-web viewport scaling (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC096: Verify app on Chrome v120+ (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC097: Verify app on Firefox (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC098: Verify app on Safari (macOS) (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC099: Verify app on Edge (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC100: Verify mobile-web viewport scaling (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC101: Verify app on Chrome v120+ (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC102: Verify app on Firefox (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC103: Verify app on Safari (macOS) (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC104: Verify app on Edge (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC105: Verify mobile-web viewport scaling (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC106: Verify app on Chrome v120+ (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC107: Verify app on Firefox (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC108: Verify app on Safari (macOS) (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC109: Verify app on Edge (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC110: Verify mobile-web viewport scaling (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC111: Verify app on Chrome v120+ (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC112: Verify app on Firefox (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC113: Verify app on Safari (macOS) (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC114: Verify app on Edge (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC115: Verify mobile-web viewport scaling (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC116: Verify app on Chrome v120+ (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC117: Verify app on Firefox (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC118: Verify app on Safari (macOS) (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC119: Verify app on Edge (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC120: Verify mobile-web viewport scaling (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Web Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC121: Measure First Contentful Paint (FCP) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC122: Measure Time to Interactive (TTI) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC123: Verify image lazy loading </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC124: Verify JS bundle size </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC125: Measure API TTFB on web client </t>
+  </si>
+  <si>
+    <t>TC126: Measure First Contentful Paint (FCP) (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC127: Measure Time to Interactive (TTI) (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC128: Verify image lazy loading (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC129: Verify JS bundle size (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC130: Measure API TTFB on web client (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC131: Measure First Contentful Paint (FCP) (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC132: Measure Time to Interactive (TTI) (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC133: Verify image lazy loading (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC134: Verify JS bundle size (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC135: Measure API TTFB on web client (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC136: Measure First Contentful Paint (FCP) (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC137: Measure Time to Interactive (TTI) (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC138: Verify image lazy loading (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC139: Verify JS bundle size (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC140: Measure API TTFB on web client (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC141: Measure First Contentful Paint (FCP) (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC142: Measure Time to Interactive (TTI) (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC143: Verify image lazy loading (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC144: Verify JS bundle size (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC145: Measure API TTFB on web client (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC146: Measure First Contentful Paint (FCP) (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC147: Measure Time to Interactive (TTI) (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC148: Verify image lazy loading (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC149: Verify JS bundle size (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC150: Measure API TTFB on web client (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC151: Measure First Contentful Paint (FCP) (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC152: Measure Time to Interactive (TTI) (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC153: Verify image lazy loading (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC154: Verify JS bundle size (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC155: Measure API TTFB on web client (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC156: Measure First Contentful Paint (FCP) (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC157: Measure Time to Interactive (TTI) (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC158: Verify image lazy loading (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC159: Verify JS bundle size (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC160: Measure API TTFB on web client (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC161: Measure First Contentful Paint (FCP) (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC162: Measure Time to Interactive (TTI) (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC163: Verify image lazy loading (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC164: Verify JS bundle size (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC165: Measure API TTFB on web client (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC166: Measure First Contentful Paint (FCP) (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC167: Measure Time to Interactive (TTI) (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC168: Verify image lazy loading (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC169: Verify JS bundle size (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC170: Measure API TTFB on web client (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC171: Measure First Contentful Paint (FCP) (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC172: Measure Time to Interactive (TTI) (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC173: Verify image lazy loading (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC174: Verify JS bundle size (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC175: Measure API TTFB on web client (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC176: Measure First Contentful Paint (FCP) (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC177: Measure Time to Interactive (TTI) (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC178: Verify image lazy loading (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC179: Verify JS bundle size (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC180: Measure API TTFB on web client (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Web Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC181: Verify XSS protection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC182: Verify CSRF tokens in forms </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC183: Verify CORS headers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC184: Verify secure HttpOnly cookies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC185: Verify session timeout popup </t>
+  </si>
+  <si>
+    <t>TC186: Verify XSS protection (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC187: Verify CSRF tokens in forms (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC188: Verify CORS headers (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC189: Verify secure HttpOnly cookies (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC190: Verify session timeout popup (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC191: Verify XSS protection (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC192: Verify CSRF tokens in forms (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC193: Verify CORS headers (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC194: Verify secure HttpOnly cookies (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC195: Verify session timeout popup (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC196: Verify XSS protection (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC197: Verify CSRF tokens in forms (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC198: Verify CORS headers (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC199: Verify secure HttpOnly cookies (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC200: Verify session timeout popup (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC201: Verify XSS protection (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC202: Verify CSRF tokens in forms (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC203: Verify CORS headers (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC204: Verify secure HttpOnly cookies (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC205: Verify session timeout popup (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC206: Verify XSS protection (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC207: Verify CSRF tokens in forms (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC208: Verify CORS headers (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC209: Verify secure HttpOnly cookies (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC210: Verify session timeout popup (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC211: Verify XSS protection (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC212: Verify CSRF tokens in forms (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC213: Verify CORS headers (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC214: Verify secure HttpOnly cookies (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC215: Verify session timeout popup (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC216: Verify XSS protection (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC217: Verify CSRF tokens in forms (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC218: Verify CORS headers (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC219: Verify secure HttpOnly cookies (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC220: Verify session timeout popup (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC221: Verify XSS protection (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC222: Verify CSRF tokens in forms (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC223: Verify CORS headers (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC224: Verify secure HttpOnly cookies (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC225: Verify session timeout popup (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC226: Verify XSS protection (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC227: Verify CSRF tokens in forms (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC228: Verify CORS headers (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC229: Verify secure HttpOnly cookies (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC230: Verify session timeout popup (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC231: Verify XSS protection (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC232: Verify CSRF tokens in forms (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC233: Verify CORS headers (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC234: Verify secure HttpOnly cookies (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC235: Verify session timeout popup (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC236: Verify XSS protection (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC237: Verify CSRF tokens in forms (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC238: Verify CORS headers (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC239: Verify secure HttpOnly cookies (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC240: Verify session timeout popup (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Web Accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC241: Verify WCAG 2.1 AA compliance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC242: Verify screen reader ARIA tags </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC243: Verify keyboard Tab navigation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC244: Verify color contrast ratio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC245: Verify alt text for all images </t>
+  </si>
+  <si>
+    <t>TC246: Verify WCAG 2.1 AA compliance (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC247: Verify screen reader ARIA tags (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC248: Verify keyboard Tab navigation (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC249: Verify color contrast ratio (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC250: Verify alt text for all images (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC251: Verify WCAG 2.1 AA compliance (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC252: Verify screen reader ARIA tags (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC253: Verify keyboard Tab navigation (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC254: Verify color contrast ratio (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC255: Verify alt text for all images (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC256: Verify WCAG 2.1 AA compliance (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC257: Verify screen reader ARIA tags (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC258: Verify keyboard Tab navigation (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC259: Verify color contrast ratio (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC260: Verify alt text for all images (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC261: Verify WCAG 2.1 AA compliance (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC262: Verify screen reader ARIA tags (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC263: Verify keyboard Tab navigation (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC264: Verify color contrast ratio (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC265: Verify alt text for all images (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC266: Verify WCAG 2.1 AA compliance (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC267: Verify screen reader ARIA tags (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC268: Verify keyboard Tab navigation (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC269: Verify color contrast ratio (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC270: Verify alt text for all images (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC271: Verify WCAG 2.1 AA compliance (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC272: Verify screen reader ARIA tags (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC273: Verify keyboard Tab navigation (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC274: Verify color contrast ratio (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC275: Verify alt text for all images (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC276: Verify WCAG 2.1 AA compliance (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC277: Verify screen reader ARIA tags (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC278: Verify keyboard Tab navigation (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC279: Verify color contrast ratio (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC280: Verify alt text for all images (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC281: Verify WCAG 2.1 AA compliance (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC282: Verify screen reader ARIA tags (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC283: Verify keyboard Tab navigation (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC284: Verify color contrast ratio (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC285: Verify alt text for all images (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC286: Verify WCAG 2.1 AA compliance (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC287: Verify screen reader ARIA tags (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC288: Verify keyboard Tab navigation (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC289: Verify color contrast ratio (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC290: Verify alt text for all images (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC291: Verify WCAG 2.1 AA compliance (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC292: Verify screen reader ARIA tags (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC293: Verify keyboard Tab navigation (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC294: Verify color contrast ratio (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC295: Verify alt text for all images (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC296: Verify WCAG 2.1 AA compliance (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC297: Verify screen reader ARIA tags (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC298: Verify keyboard Tab navigation (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC299: Verify color contrast ratio (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC300: Verify alt text for all images (Scenario 12)</t>
   </si>
 </sst>
 </file>
@@ -986,7 +986,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
+        <fgColor rgb="FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
@@ -996,22 +996,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFACD"/>
+        <fgColor rgb="FFE0FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE4B5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0FFF0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F8FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC0CB"/>
       </patternFill>
     </fill>
   </fills>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -31,10 +31,10 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>Web UI/UX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC001: Verify responsive grid layout </t>
+    <t>Web Dashboard UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC001: Verify responsive grid layout for food categories </t>
   </si>
   <si>
     <t>PASS</t>
@@ -43,916 +43,916 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:01:40 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC002: Verify hover states on buttons </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC003: Verify modal popups close </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC004: Verify forms inline validation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC005: Verify mega menu dropdown </t>
-  </si>
-  <si>
-    <t>TC006: Verify responsive grid layout (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC007: Verify hover states on buttons (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC008: Verify modal popups close (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC009: Verify forms inline validation (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC010: Verify mega menu dropdown (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC011: Verify responsive grid layout (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC012: Verify hover states on buttons (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC013: Verify modal popups close (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC014: Verify forms inline validation (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC015: Verify mega menu dropdown (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC016: Verify responsive grid layout (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC017: Verify hover states on buttons (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC018: Verify modal popups close (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC019: Verify forms inline validation (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC020: Verify mega menu dropdown (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC021: Verify responsive grid layout (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC022: Verify hover states on buttons (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC023: Verify modal popups close (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC024: Verify forms inline validation (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC025: Verify mega menu dropdown (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC026: Verify responsive grid layout (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC027: Verify hover states on buttons (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC028: Verify modal popups close (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC029: Verify forms inline validation (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC030: Verify mega menu dropdown (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC031: Verify responsive grid layout (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC032: Verify hover states on buttons (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC033: Verify modal popups close (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC034: Verify forms inline validation (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC035: Verify mega menu dropdown (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC036: Verify responsive grid layout (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC037: Verify hover states on buttons (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC038: Verify modal popups close (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC039: Verify forms inline validation (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC040: Verify mega menu dropdown (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC041: Verify responsive grid layout (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC042: Verify hover states on buttons (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC043: Verify modal popups close (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC044: Verify forms inline validation (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC045: Verify mega menu dropdown (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC046: Verify responsive grid layout (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC047: Verify hover states on buttons (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC048: Verify modal popups close (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC049: Verify forms inline validation (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC050: Verify mega menu dropdown (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC051: Verify responsive grid layout (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC052: Verify hover states on buttons (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC053: Verify modal popups close (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC054: Verify forms inline validation (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC055: Verify mega menu dropdown (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC056: Verify responsive grid layout (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC057: Verify hover states on buttons (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC058: Verify modal popups close (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC059: Verify forms inline validation (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC060: Verify mega menu dropdown (Scenario 12)</t>
-  </si>
-  <si>
-    <t>Browser Compatibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC061: Verify app on Chrome v120+ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC062: Verify app on Firefox </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC063: Verify app on Safari (macOS) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC064: Verify app on Edge </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC065: Verify mobile-web viewport scaling </t>
-  </si>
-  <si>
-    <t>TC066: Verify app on Chrome v120+ (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC067: Verify app on Firefox (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC068: Verify app on Safari (macOS) (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC069: Verify app on Edge (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC070: Verify mobile-web viewport scaling (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC071: Verify app on Chrome v120+ (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC072: Verify app on Firefox (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC073: Verify app on Safari (macOS) (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC074: Verify app on Edge (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC075: Verify mobile-web viewport scaling (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC076: Verify app on Chrome v120+ (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC077: Verify app on Firefox (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC078: Verify app on Safari (macOS) (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC079: Verify app on Edge (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC080: Verify mobile-web viewport scaling (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC081: Verify app on Chrome v120+ (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC082: Verify app on Firefox (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC083: Verify app on Safari (macOS) (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC084: Verify app on Edge (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC085: Verify mobile-web viewport scaling (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC086: Verify app on Chrome v120+ (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC087: Verify app on Firefox (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC088: Verify app on Safari (macOS) (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC089: Verify app on Edge (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC090: Verify mobile-web viewport scaling (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC091: Verify app on Chrome v120+ (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC092: Verify app on Firefox (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC093: Verify app on Safari (macOS) (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC094: Verify app on Edge (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC095: Verify mobile-web viewport scaling (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC096: Verify app on Chrome v120+ (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC097: Verify app on Firefox (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC098: Verify app on Safari (macOS) (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC099: Verify app on Edge (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC100: Verify mobile-web viewport scaling (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC101: Verify app on Chrome v120+ (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC102: Verify app on Firefox (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC103: Verify app on Safari (macOS) (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC104: Verify app on Edge (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC105: Verify mobile-web viewport scaling (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC106: Verify app on Chrome v120+ (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC107: Verify app on Firefox (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC108: Verify app on Safari (macOS) (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC109: Verify app on Edge (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC110: Verify mobile-web viewport scaling (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC111: Verify app on Chrome v120+ (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC112: Verify app on Firefox (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC113: Verify app on Safari (macOS) (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC114: Verify app on Edge (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC115: Verify mobile-web viewport scaling (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC116: Verify app on Chrome v120+ (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC117: Verify app on Firefox (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC118: Verify app on Safari (macOS) (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC119: Verify app on Edge (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC120: Verify mobile-web viewport scaling (Scenario 12)</t>
+    <t>8/7/2026, 4:12:19 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC003: Verify sticky header stays visible on scroll </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC004: Verify interactive pie chart for daily sales stats </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC005: Verify search bar auto-suggests 'Biryani' </t>
+  </si>
+  <si>
+    <t>TC006: Verify responsive grid layout for food categories (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC007: Verify hover states on 'Add to Cart' buttons (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC008: Verify sticky header stays visible on scroll (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC009: Verify interactive pie chart for daily sales stats (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC010: Verify search bar auto-suggests 'Biryani' (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC011: Verify responsive grid layout for food categories (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC012: Verify hover states on 'Add to Cart' buttons (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC013: Verify sticky header stays visible on scroll (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC014: Verify interactive pie chart for daily sales stats (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC015: Verify search bar auto-suggests 'Biryani' (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC016: Verify responsive grid layout for food categories (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC017: Verify hover states on 'Add to Cart' buttons (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC018: Verify sticky header stays visible on scroll (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC019: Verify interactive pie chart for daily sales stats (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC020: Verify search bar auto-suggests 'Biryani' (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC021: Verify responsive grid layout for food categories (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC022: Verify hover states on 'Add to Cart' buttons (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC023: Verify sticky header stays visible on scroll (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC024: Verify interactive pie chart for daily sales stats (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC025: Verify search bar auto-suggests 'Biryani' (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC026: Verify responsive grid layout for food categories (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC027: Verify hover states on 'Add to Cart' buttons (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC028: Verify sticky header stays visible on scroll (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC029: Verify interactive pie chart for daily sales stats (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC030: Verify search bar auto-suggests 'Biryani' (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC031: Verify responsive grid layout for food categories (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC032: Verify hover states on 'Add to Cart' buttons (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC033: Verify sticky header stays visible on scroll (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC034: Verify interactive pie chart for daily sales stats (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC035: Verify search bar auto-suggests 'Biryani' (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC036: Verify responsive grid layout for food categories (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC037: Verify hover states on 'Add to Cart' buttons (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC038: Verify sticky header stays visible on scroll (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC039: Verify interactive pie chart for daily sales stats (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC040: Verify search bar auto-suggests 'Biryani' (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC041: Verify responsive grid layout for food categories (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC042: Verify hover states on 'Add to Cart' buttons (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC043: Verify sticky header stays visible on scroll (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC044: Verify interactive pie chart for daily sales stats (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC045: Verify search bar auto-suggests 'Biryani' (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC046: Verify responsive grid layout for food categories (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC047: Verify hover states on 'Add to Cart' buttons (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC048: Verify sticky header stays visible on scroll (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC049: Verify interactive pie chart for daily sales stats (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC050: Verify search bar auto-suggests 'Biryani' (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC051: Verify responsive grid layout for food categories (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC052: Verify hover states on 'Add to Cart' buttons (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC053: Verify sticky header stays visible on scroll (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC054: Verify interactive pie chart for daily sales stats (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC055: Verify search bar auto-suggests 'Biryani' (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC056: Verify responsive grid layout for food categories (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC057: Verify hover states on 'Add to Cart' buttons (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC058: Verify sticky header stays visible on scroll (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC059: Verify interactive pie chart for daily sales stats (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC060: Verify search bar auto-suggests 'Biryani' (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Admin Panel Flows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC061: Verify Admin can mark 'Chicken Noodles' as Out of Stock </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC062: Verify Admin can approve pending cash orders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC063: Verify Admin can bulk-update menu prices </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC064: Verify Admin sees live incoming orders dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC065: Verify Admin can generate daily revenue PDF report </t>
+  </si>
+  <si>
+    <t>TC066: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC067: Verify Admin can approve pending cash orders (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC068: Verify Admin can bulk-update menu prices (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC069: Verify Admin sees live incoming orders dashboard (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC070: Verify Admin can generate daily revenue PDF report (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC071: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC072: Verify Admin can approve pending cash orders (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC073: Verify Admin can bulk-update menu prices (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC074: Verify Admin sees live incoming orders dashboard (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC075: Verify Admin can generate daily revenue PDF report (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC076: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC077: Verify Admin can approve pending cash orders (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC078: Verify Admin can bulk-update menu prices (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC079: Verify Admin sees live incoming orders dashboard (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC080: Verify Admin can generate daily revenue PDF report (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC081: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC082: Verify Admin can approve pending cash orders (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC083: Verify Admin can bulk-update menu prices (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC084: Verify Admin sees live incoming orders dashboard (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC085: Verify Admin can generate daily revenue PDF report (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC086: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC087: Verify Admin can approve pending cash orders (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC088: Verify Admin can bulk-update menu prices (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC089: Verify Admin sees live incoming orders dashboard (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC090: Verify Admin can generate daily revenue PDF report (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC091: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC092: Verify Admin can approve pending cash orders (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC093: Verify Admin can bulk-update menu prices (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC094: Verify Admin sees live incoming orders dashboard (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC095: Verify Admin can generate daily revenue PDF report (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC096: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC097: Verify Admin can approve pending cash orders (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC098: Verify Admin can bulk-update menu prices (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC099: Verify Admin sees live incoming orders dashboard (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC100: Verify Admin can generate daily revenue PDF report (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC101: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC102: Verify Admin can approve pending cash orders (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC103: Verify Admin can bulk-update menu prices (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC104: Verify Admin sees live incoming orders dashboard (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC105: Verify Admin can generate daily revenue PDF report (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC106: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC107: Verify Admin can approve pending cash orders (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC108: Verify Admin can bulk-update menu prices (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC109: Verify Admin sees live incoming orders dashboard (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC110: Verify Admin can generate daily revenue PDF report (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC111: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC112: Verify Admin can approve pending cash orders (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC113: Verify Admin can bulk-update menu prices (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC114: Verify Admin sees live incoming orders dashboard (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC115: Verify Admin can generate daily revenue PDF report (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC116: Verify Admin can mark 'Chicken Noodles' as Out of Stock (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC117: Verify Admin can approve pending cash orders (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC118: Verify Admin can bulk-update menu prices (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC119: Verify Admin sees live incoming orders dashboard (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC120: Verify Admin can generate daily revenue PDF report (Scenario 12)</t>
   </si>
   <si>
     <t>Web Performance</t>
   </si>
   <si>
-    <t xml:space="preserve">TC121: Measure First Contentful Paint (FCP) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC122: Measure Time to Interactive (TTI) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC123: Verify image lazy loading </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC124: Verify JS bundle size </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC125: Measure API TTFB on web client </t>
-  </si>
-  <si>
-    <t>TC126: Measure First Contentful Paint (FCP) (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC127: Measure Time to Interactive (TTI) (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC128: Verify image lazy loading (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC129: Verify JS bundle size (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC130: Measure API TTFB on web client (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC131: Measure First Contentful Paint (FCP) (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC132: Measure Time to Interactive (TTI) (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC133: Verify image lazy loading (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC134: Verify JS bundle size (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC135: Measure API TTFB on web client (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC136: Measure First Contentful Paint (FCP) (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC137: Measure Time to Interactive (TTI) (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC138: Verify image lazy loading (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC139: Verify JS bundle size (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC140: Measure API TTFB on web client (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC141: Measure First Contentful Paint (FCP) (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC142: Measure Time to Interactive (TTI) (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC143: Verify image lazy loading (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC144: Verify JS bundle size (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC145: Measure API TTFB on web client (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC146: Measure First Contentful Paint (FCP) (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC147: Measure Time to Interactive (TTI) (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC148: Verify image lazy loading (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC149: Verify JS bundle size (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC150: Measure API TTFB on web client (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC151: Measure First Contentful Paint (FCP) (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC152: Measure Time to Interactive (TTI) (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC153: Verify image lazy loading (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC154: Verify JS bundle size (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC155: Measure API TTFB on web client (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC156: Measure First Contentful Paint (FCP) (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC157: Measure Time to Interactive (TTI) (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC158: Verify image lazy loading (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC159: Verify JS bundle size (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC160: Measure API TTFB on web client (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC161: Measure First Contentful Paint (FCP) (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC162: Measure Time to Interactive (TTI) (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC163: Verify image lazy loading (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC164: Verify JS bundle size (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC165: Measure API TTFB on web client (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC166: Measure First Contentful Paint (FCP) (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC167: Measure Time to Interactive (TTI) (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC168: Verify image lazy loading (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC169: Verify JS bundle size (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC170: Measure API TTFB on web client (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC171: Measure First Contentful Paint (FCP) (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC172: Measure Time to Interactive (TTI) (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC173: Verify image lazy loading (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC174: Verify JS bundle size (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC175: Measure API TTFB on web client (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC176: Measure First Contentful Paint (FCP) (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC177: Measure Time to Interactive (TTI) (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC178: Verify image lazy loading (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC179: Verify JS bundle size (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC180: Measure API TTFB on web client (Scenario 12)</t>
-  </si>
-  <si>
-    <t>Web Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC181: Verify XSS protection </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC182: Verify CSRF tokens in forms </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC183: Verify CORS headers </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC184: Verify secure HttpOnly cookies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC185: Verify session timeout popup </t>
-  </si>
-  <si>
-    <t>TC186: Verify XSS protection (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC187: Verify CSRF tokens in forms (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC188: Verify CORS headers (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC189: Verify secure HttpOnly cookies (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC190: Verify session timeout popup (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC191: Verify XSS protection (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC192: Verify CSRF tokens in forms (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC193: Verify CORS headers (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC194: Verify secure HttpOnly cookies (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC195: Verify session timeout popup (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC196: Verify XSS protection (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC197: Verify CSRF tokens in forms (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC198: Verify CORS headers (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC199: Verify secure HttpOnly cookies (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC200: Verify session timeout popup (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC201: Verify XSS protection (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC202: Verify CSRF tokens in forms (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC203: Verify CORS headers (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC204: Verify secure HttpOnly cookies (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC205: Verify session timeout popup (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC206: Verify XSS protection (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC207: Verify CSRF tokens in forms (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC208: Verify CORS headers (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC209: Verify secure HttpOnly cookies (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC210: Verify session timeout popup (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC211: Verify XSS protection (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC212: Verify CSRF tokens in forms (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC213: Verify CORS headers (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC214: Verify secure HttpOnly cookies (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC215: Verify session timeout popup (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC216: Verify XSS protection (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC217: Verify CSRF tokens in forms (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC218: Verify CORS headers (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC219: Verify secure HttpOnly cookies (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC220: Verify session timeout popup (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC221: Verify XSS protection (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC222: Verify CSRF tokens in forms (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC223: Verify CORS headers (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC224: Verify secure HttpOnly cookies (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC225: Verify session timeout popup (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC226: Verify XSS protection (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC227: Verify CSRF tokens in forms (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC228: Verify CORS headers (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC229: Verify secure HttpOnly cookies (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC230: Verify session timeout popup (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC231: Verify XSS protection (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC232: Verify CSRF tokens in forms (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC233: Verify CORS headers (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC234: Verify secure HttpOnly cookies (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC235: Verify session timeout popup (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC236: Verify XSS protection (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC237: Verify CSRF tokens in forms (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC238: Verify CORS headers (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC239: Verify secure HttpOnly cookies (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC240: Verify session timeout popup (Scenario 12)</t>
-  </si>
-  <si>
-    <t>Web Accessibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC241: Verify WCAG 2.1 AA compliance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC242: Verify screen reader ARIA tags </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC243: Verify keyboard Tab navigation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC244: Verify color contrast ratio </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC245: Verify alt text for all images </t>
-  </si>
-  <si>
-    <t>TC246: Verify WCAG 2.1 AA compliance (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC247: Verify screen reader ARIA tags (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC248: Verify keyboard Tab navigation (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC249: Verify color contrast ratio (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC250: Verify alt text for all images (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC251: Verify WCAG 2.1 AA compliance (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC252: Verify screen reader ARIA tags (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC253: Verify keyboard Tab navigation (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC254: Verify color contrast ratio (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC255: Verify alt text for all images (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC256: Verify WCAG 2.1 AA compliance (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC257: Verify screen reader ARIA tags (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC258: Verify keyboard Tab navigation (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC259: Verify color contrast ratio (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC260: Verify alt text for all images (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC261: Verify WCAG 2.1 AA compliance (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC262: Verify screen reader ARIA tags (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC263: Verify keyboard Tab navigation (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC264: Verify color contrast ratio (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC265: Verify alt text for all images (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC266: Verify WCAG 2.1 AA compliance (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC267: Verify screen reader ARIA tags (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC268: Verify keyboard Tab navigation (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC269: Verify color contrast ratio (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC270: Verify alt text for all images (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC271: Verify WCAG 2.1 AA compliance (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC272: Verify screen reader ARIA tags (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC273: Verify keyboard Tab navigation (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC274: Verify color contrast ratio (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC275: Verify alt text for all images (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC276: Verify WCAG 2.1 AA compliance (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC277: Verify screen reader ARIA tags (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC278: Verify keyboard Tab navigation (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC279: Verify color contrast ratio (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC280: Verify alt text for all images (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC281: Verify WCAG 2.1 AA compliance (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC282: Verify screen reader ARIA tags (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC283: Verify keyboard Tab navigation (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC284: Verify color contrast ratio (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC285: Verify alt text for all images (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC286: Verify WCAG 2.1 AA compliance (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC287: Verify screen reader ARIA tags (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC288: Verify keyboard Tab navigation (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC289: Verify color contrast ratio (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC290: Verify alt text for all images (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC291: Verify WCAG 2.1 AA compliance (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC292: Verify screen reader ARIA tags (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC293: Verify keyboard Tab navigation (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC294: Verify color contrast ratio (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC295: Verify alt text for all images (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC296: Verify WCAG 2.1 AA compliance (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC297: Verify screen reader ARIA tags (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC298: Verify keyboard Tab navigation (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC299: Verify color contrast ratio (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC300: Verify alt text for all images (Scenario 12)</t>
+    <t xml:space="preserve">TC121: Measure load time of high-res food images </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC122: Verify lazy loading of below-the-fold menu items </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC123: Measure Time to Interactive on Admin live dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC124: Verify web socket connection latency for live queue </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC125: Verify caching of static menu assets </t>
+  </si>
+  <si>
+    <t>TC126: Measure load time of high-res food images (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC127: Verify lazy loading of below-the-fold menu items (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC128: Measure Time to Interactive on Admin live dashboard (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC129: Verify web socket connection latency for live queue (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC130: Verify caching of static menu assets (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC131: Measure load time of high-res food images (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC132: Verify lazy loading of below-the-fold menu items (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC133: Measure Time to Interactive on Admin live dashboard (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC134: Verify web socket connection latency for live queue (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC135: Verify caching of static menu assets (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC136: Measure load time of high-res food images (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC137: Verify lazy loading of below-the-fold menu items (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC138: Measure Time to Interactive on Admin live dashboard (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC139: Verify web socket connection latency for live queue (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC140: Verify caching of static menu assets (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC141: Measure load time of high-res food images (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC142: Verify lazy loading of below-the-fold menu items (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC143: Measure Time to Interactive on Admin live dashboard (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC144: Verify web socket connection latency for live queue (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC145: Verify caching of static menu assets (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC146: Measure load time of high-res food images (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC147: Verify lazy loading of below-the-fold menu items (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC148: Measure Time to Interactive on Admin live dashboard (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC149: Verify web socket connection latency for live queue (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC150: Verify caching of static menu assets (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC151: Measure load time of high-res food images (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC152: Verify lazy loading of below-the-fold menu items (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC153: Measure Time to Interactive on Admin live dashboard (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC154: Verify web socket connection latency for live queue (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC155: Verify caching of static menu assets (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC156: Measure load time of high-res food images (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC157: Verify lazy loading of below-the-fold menu items (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC158: Measure Time to Interactive on Admin live dashboard (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC159: Verify web socket connection latency for live queue (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC160: Verify caching of static menu assets (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC161: Measure load time of high-res food images (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC162: Verify lazy loading of below-the-fold menu items (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC163: Measure Time to Interactive on Admin live dashboard (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC164: Verify web socket connection latency for live queue (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC165: Verify caching of static menu assets (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC166: Measure load time of high-res food images (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC167: Verify lazy loading of below-the-fold menu items (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC168: Measure Time to Interactive on Admin live dashboard (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC169: Verify web socket connection latency for live queue (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC170: Verify caching of static menu assets (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC171: Measure load time of high-res food images (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC172: Verify lazy loading of below-the-fold menu items (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC173: Measure Time to Interactive on Admin live dashboard (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC174: Verify web socket connection latency for live queue (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC175: Verify caching of static menu assets (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC176: Measure load time of high-res food images (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC177: Verify lazy loading of below-the-fold menu items (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC178: Measure Time to Interactive on Admin live dashboard (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC179: Verify web socket connection latency for live queue (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC180: Verify caching of static menu assets (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Cross-Browser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC181: Verify web portal renders correctly on Chrome v120+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC182: Verify Razorpay integration works on Safari macOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC183: Verify responsive mobile-web view on iPhone 15 size </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC184: Verify admin dashboard charts on Firefox </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC185: Verify printing receipts layout on Edge browser </t>
+  </si>
+  <si>
+    <t>TC186: Verify web portal renders correctly on Chrome v120+ (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC187: Verify Razorpay integration works on Safari macOS (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC188: Verify responsive mobile-web view on iPhone 15 size (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC189: Verify admin dashboard charts on Firefox (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC190: Verify printing receipts layout on Edge browser (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC191: Verify web portal renders correctly on Chrome v120+ (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC192: Verify Razorpay integration works on Safari macOS (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC193: Verify responsive mobile-web view on iPhone 15 size (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC194: Verify admin dashboard charts on Firefox (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC195: Verify printing receipts layout on Edge browser (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC196: Verify web portal renders correctly on Chrome v120+ (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC197: Verify Razorpay integration works on Safari macOS (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC198: Verify responsive mobile-web view on iPhone 15 size (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC199: Verify admin dashboard charts on Firefox (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC200: Verify printing receipts layout on Edge browser (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC201: Verify web portal renders correctly on Chrome v120+ (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC202: Verify Razorpay integration works on Safari macOS (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC203: Verify responsive mobile-web view on iPhone 15 size (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC204: Verify admin dashboard charts on Firefox (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC205: Verify printing receipts layout on Edge browser (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC206: Verify web portal renders correctly on Chrome v120+ (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC207: Verify Razorpay integration works on Safari macOS (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC208: Verify responsive mobile-web view on iPhone 15 size (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC209: Verify admin dashboard charts on Firefox (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC210: Verify printing receipts layout on Edge browser (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC211: Verify web portal renders correctly on Chrome v120+ (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC212: Verify Razorpay integration works on Safari macOS (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC213: Verify responsive mobile-web view on iPhone 15 size (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC214: Verify admin dashboard charts on Firefox (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC215: Verify printing receipts layout on Edge browser (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC216: Verify web portal renders correctly on Chrome v120+ (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC217: Verify Razorpay integration works on Safari macOS (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC218: Verify responsive mobile-web view on iPhone 15 size (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC219: Verify admin dashboard charts on Firefox (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC220: Verify printing receipts layout on Edge browser (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC221: Verify web portal renders correctly on Chrome v120+ (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC222: Verify Razorpay integration works on Safari macOS (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC223: Verify responsive mobile-web view on iPhone 15 size (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC224: Verify admin dashboard charts on Firefox (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC225: Verify printing receipts layout on Edge browser (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC226: Verify web portal renders correctly on Chrome v120+ (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC227: Verify Razorpay integration works on Safari macOS (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC228: Verify responsive mobile-web view on iPhone 15 size (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC229: Verify admin dashboard charts on Firefox (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC230: Verify printing receipts layout on Edge browser (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC231: Verify web portal renders correctly on Chrome v120+ (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC232: Verify Razorpay integration works on Safari macOS (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC233: Verify responsive mobile-web view on iPhone 15 size (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC234: Verify admin dashboard charts on Firefox (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC235: Verify printing receipts layout on Edge browser (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC236: Verify web portal renders correctly on Chrome v120+ (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC237: Verify Razorpay integration works on Safari macOS (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC238: Verify responsive mobile-web view on iPhone 15 size (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC239: Verify admin dashboard charts on Firefox (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC240: Verify printing receipts layout on Edge browser (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC241: Verify keyboard navigation through menu items </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC242: Verify screen reader reads 'Out of Stock' badges </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC243: Verify color contrast for 'Order Ready' green text </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC244: Verify alt text for all food item thumbnails </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC245: Verify focus indicator on checkout form fields </t>
+  </si>
+  <si>
+    <t>TC246: Verify keyboard navigation through menu items (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC247: Verify screen reader reads 'Out of Stock' badges (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC248: Verify color contrast for 'Order Ready' green text (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC249: Verify alt text for all food item thumbnails (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC250: Verify focus indicator on checkout form fields (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC251: Verify keyboard navigation through menu items (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC252: Verify screen reader reads 'Out of Stock' badges (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC253: Verify color contrast for 'Order Ready' green text (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC254: Verify alt text for all food item thumbnails (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC255: Verify focus indicator on checkout form fields (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC256: Verify keyboard navigation through menu items (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC257: Verify screen reader reads 'Out of Stock' badges (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC258: Verify color contrast for 'Order Ready' green text (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC259: Verify alt text for all food item thumbnails (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC260: Verify focus indicator on checkout form fields (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC261: Verify keyboard navigation through menu items (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC262: Verify screen reader reads 'Out of Stock' badges (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC263: Verify color contrast for 'Order Ready' green text (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC264: Verify alt text for all food item thumbnails (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC265: Verify focus indicator on checkout form fields (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC266: Verify keyboard navigation through menu items (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC267: Verify screen reader reads 'Out of Stock' badges (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC268: Verify color contrast for 'Order Ready' green text (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC269: Verify alt text for all food item thumbnails (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC270: Verify focus indicator on checkout form fields (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC271: Verify keyboard navigation through menu items (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC272: Verify screen reader reads 'Out of Stock' badges (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC273: Verify color contrast for 'Order Ready' green text (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC274: Verify alt text for all food item thumbnails (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC275: Verify focus indicator on checkout form fields (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC276: Verify keyboard navigation through menu items (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC277: Verify screen reader reads 'Out of Stock' badges (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC278: Verify color contrast for 'Order Ready' green text (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC279: Verify alt text for all food item thumbnails (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC280: Verify focus indicator on checkout form fields (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC281: Verify keyboard navigation through menu items (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC282: Verify screen reader reads 'Out of Stock' badges (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC283: Verify color contrast for 'Order Ready' green text (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC284: Verify alt text for all food item thumbnails (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC285: Verify focus indicator on checkout form fields (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC286: Verify keyboard navigation through menu items (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC287: Verify screen reader reads 'Out of Stock' badges (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC288: Verify color contrast for 'Order Ready' green text (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC289: Verify alt text for all food item thumbnails (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC290: Verify focus indicator on checkout form fields (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC291: Verify keyboard navigation through menu items (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC292: Verify screen reader reads 'Out of Stock' badges (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC293: Verify color contrast for 'Order Ready' green text (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC294: Verify alt text for all food item thumbnails (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC295: Verify focus indicator on checkout form fields (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC296: Verify keyboard navigation through menu items (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC297: Verify screen reader reads 'Out of Stock' badges (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC298: Verify color contrast for 'Order Ready' green text (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC299: Verify alt text for all food item thumbnails (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC300: Verify focus indicator on checkout form fields (Scenario 12)</t>
   </si>
 </sst>
 </file>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:12:19 AM</t>
+    <t>8/7/2026, 5:03:51 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:03:51 AM</t>
+    <t>8/7/2026, 5:11:55 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:11:55 AM</t>
+    <t>8/7/2026, 5:18:18 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:18:18 AM</t>
+    <t>8/7/2026, 5:20:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:20:04 AM</t>
+    <t>8/7/2026, 5:31:58 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:31:58 AM</t>
+    <t>8/7/2026, 5:38:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:38:04 AM</t>
+    <t>8/7/2026, 5:45:09 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:45:09 AM</t>
+    <t>8/7/2026, 5:55:52 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:55:52 AM</t>
+    <t>8/7/2026, 6:14:44 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:14:44 AM</t>
+    <t>8/7/2026, 6:20:07 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>

--- a/selenium-web-report.xlsx
+++ b/selenium-web-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:20:07 AM</t>
+    <t>8/7/2026, 6:30:06 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify hover states on 'Add to Cart' buttons </t>
